--- a/astro-site/public/dl/plan-negocio-tapas-bar/plan-financiero-tapas-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-tapas-bar/plan-financiero-tapas-bar.xlsx
@@ -1333,7 +1333,7 @@
         <v>1.2444444444444445</v>
       </c>
       <c r="C50" t="str">
-        <f>IFERROR("Son "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;","&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" servicios por plaza y día sobre las "&amp;TEXT($B$51,"0")&amp;" plazas de la celda de arriba. El documento de este plan pide 1,8 servicios por cubierto en el almuerzo y 1,5 en la cena, que sumados son unas 3,3 rotaciones al día: por encima del techo de 3 que trae por defecto la hoja «Punto Equilibrio». Ajusta ese techo a tu horario y a tu aforo reales antes de dar por buena ninguna de las dos cifras.","")</f>
+        <f>IFERROR("Son "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;","&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" servicios por plaza y día sobre las "&amp;TEXT($B$51,"0")&amp;" plazas de la celda de arriba. El documento de este plan pide 1,8 servicios por cubierto en el almuerzo y 1,5 en la cena, que sumados son unas 3,3 rotaciones al día: por encima del techo de 3 que trae por defecto la hoja «Punto "&amp;"Equilibrio». Ajusta ese techo a tu horario y a tu aforo reales antes de dar por buena ninguna de las dos cifras.","")</f>
         <v>Son 1,2 servicios por plaza y día sobre las 45 plazas de la celda de arriba. El documento de este plan pide 1,8 servicios por cubierto en el almuerzo y 1,5 en la cena, que sumados son unas 3,3 rotaciones al día: por encima del techo de 3 que trae por defecto la hoja «Punto Equilibrio». Ajusta ese techo a tu horario y a tu aforo reales antes de dar por buena ninguna de las dos cifras.</v>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>0.029022918975184425</v>
       </c>
       <c r="D27" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación + extracciones, Grifos cerveza + instalación, Decoración + iluminación ambiente y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación + extracciones, Grifos cerveza + instalación, "&amp;"Decoración + iluminación ambiente y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación + extracciones, Grifos cerveza + instalación, Decoración + iluminación ambiente y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2300,7 +2300,7 @@
         <v>20989.5</v>
       </c>
       <c r="D32" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
         <v>10145.0</v>
       </c>
       <c r="D37" s="38" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (clasificada), Marketing lanzamiento, Stock inicial (producto, vinos, cervezas), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (clasificada), Marketing lanzamiento, Stock inicial (producto, vinos, cervezas), Fianza del alquiler, Alquiler de los meses previos a la "&amp;"apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (clasificada), Marketing lanzamiento, Stock inicial (producto, vinos, cervezas), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 62377 € de los 153327 € de inversión.</v>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>

--- a/astro-site/public/dl/plan-negocio-tapas-bar/plan-financiero-tapas-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-tapas-bar/plan-financiero-tapas-bar.xlsx
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-tapas-bar/plan-financiero-tapas-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-tapas-bar/plan-financiero-tapas-bar.xlsx
@@ -1333,7 +1333,7 @@
         <v>1.2444444444444445</v>
       </c>
       <c r="C50" t="str">
-        <f>IFERROR("Son "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;","&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" servicios por plaza y día sobre las "&amp;TEXT($B$51,"0")&amp;" plazas de la celda de arriba. El documento de este plan pide 1,8 servicios por cubierto en el almuerzo y 1,5 en la cena, que sumados son unas 3,3 rotaciones al día: por encima del techo de 3 que trae por defecto la hoja «Punto Equilibrio». Ajusta ese techo a tu horario y a tu aforo reales antes de dar por buena ninguna de las dos cifras.","")</f>
+        <f>IFERROR("Son "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;","&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" servicios por plaza y día sobre las "&amp;TEXT($B$51,"0")&amp;" plazas de la celda de arriba. El documento de este plan pide 1,8 servicios por cubierto en el almuerzo y 1,5 en la cena, que sumados son unas 3,3 rotaciones al día: por encima del techo de 3 que trae por defecto la hoja «Punto "&amp;"Equilibrio». Ajusta ese techo a tu horario y a tu aforo reales antes de dar por buena ninguna de las dos cifras.","")</f>
         <v>Son 1,2 servicios por plaza y día sobre las 45 plazas de la celda de arriba. El documento de este plan pide 1,8 servicios por cubierto en el almuerzo y 1,5 en la cena, que sumados son unas 3,3 rotaciones al día: por encima del techo de 3 que trae por defecto la hoja «Punto Equilibrio». Ajusta ese techo a tu horario y a tu aforo reales antes de dar por buena ninguna de las dos cifras.</v>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>0.029022918975184425</v>
       </c>
       <c r="D27" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación + extracciones, Grifos cerveza + instalación, Decoración + iluminación ambiente y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación + extracciones, Grifos cerveza + instalación, "&amp;"Decoración + iluminación ambiente y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación + extracciones, Grifos cerveza + instalación, Decoración + iluminación ambiente y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2300,7 +2300,7 @@
         <v>20989.5</v>
       </c>
       <c r="D32" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
         <v>10145.0</v>
       </c>
       <c r="D37" s="38" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (clasificada), Marketing lanzamiento, Stock inicial (producto, vinos, cervezas), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (clasificada), Marketing lanzamiento, Stock inicial (producto, vinos, cervezas), Fianza del alquiler, Alquiler de los meses previos a la "&amp;"apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (clasificada), Marketing lanzamiento, Stock inicial (producto, vinos, cervezas), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 62377 € de los 153327 € de inversión.</v>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
